--- a/ValueSet-i2x-pneumo-bio.xlsx
+++ b/ValueSet-i2x-pneumo-bio.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-i2x-pneumo-bio.xlsx
+++ b/ValueSet-i2x-pneumo-bio.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Jeu de biologies d'intérêt pour la télésurveillance des maladies respiratoires</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -81,6 +78,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Valueset for significant laboratory results in the scope of the 'Vers Un Souffle Nouveau' project</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -102,7 +102,7 @@
     <t>718-7</t>
   </si>
   <si>
-    <t>Hémoglobine</t>
+    <t>Hemoglobin</t>
   </si>
   <si>
     <t>1988-5</t>
@@ -114,25 +114,25 @@
     <t>26449-9</t>
   </si>
   <si>
-    <t>Éosinophiles</t>
+    <t>Eosinophils</t>
   </si>
   <si>
     <t>38483-4</t>
   </si>
   <si>
-    <t>Créatinine</t>
+    <t>Creatinin</t>
   </si>
   <si>
     <t>70969-1</t>
   </si>
   <si>
-    <t>Taux de filtration glomérulaire parmi la population masculine</t>
+    <t>Glomerular filtration rate for male</t>
   </si>
   <si>
     <t>50044-7</t>
   </si>
   <si>
-    <t>Taux de filtration glomérulaire parmi la population féminine</t>
+    <t>Glomerular filtration rate for female</t>
   </si>
   <si>
     <t>System URI</t>
@@ -315,62 +315,60 @@
       <c r="A5" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>9</v>
-      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>13</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>15</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>17</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>19</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -414,7 +412,7 @@
         <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2">
@@ -467,10 +465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">

--- a/ValueSet-i2x-pneumo-bio.xlsx
+++ b/ValueSet-i2x-pneumo-bio.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-i2x-pneumo-bio.xlsx
+++ b/ValueSet-i2x-pneumo-bio.xlsx
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>RM@H IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
+    <t>VUNS IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
   </si>
   <si>
     <t>Immutable</t>
